--- a/Documents/ODMAP-Table.xlsx
+++ b/Documents/ODMAP-Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarahhart/Library/CloudStorage/GoogleDrive-sarahjanehart13@gmail.com/My Drive/JOB/RESEARCH/Analyses/AspenHabitat/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0240C27-1BB0-884E-851A-71121292910D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D719F936-5EE1-DE48-8ED1-AC38C85D2928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1720" windowWidth="30240" windowHeight="17920" xr2:uid="{13C9FE07-A4C9-0B4A-BF1F-85133AC3EB69}"/>
   </bookViews>
@@ -291,27 +291,6 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>Contact email:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> sarah.hart@colostate.edu</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
       <t>Spatial resolution</t>
     </r>
     <r>
@@ -1085,6 +1064,54 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Title: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Climate-driven decreases in aspen's distribution and opportunities for future expansion across the Southern Rocky Mountains</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Data source</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: Aspen presence-absence data at 10x10 m spatial resolution were obtained from Cook et al. (2024).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Absence data: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>The Cook et al. (2024) map consists of both presence and absence data.</t>
+    </r>
+  </si>
+  <si>
+    <t>To avoid collinearity between climate predictors, we initially screened the 34 climatic variables at their original resolution (i.e. 1 x 1 km). To this end, we calculated pairwise correlation coefficients and when |r|&gt;0.75, we removed variables based on existing research (Table 5). Where evidence was similar, we used univariate random forest (RF) models to evaluate the potential explanatory power of each predictor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using the R package DALEX (Biecek 2018), we determined variable importance using a model-agnostic permutation-based approach. In this approach, each variable is randomized and then AUC statistic is compared with the AUC for the full model (where data has not been randomized). We evaluated the relationship between aspen presence and each predictor variable using accumulated local effects (ALE) profiles, which were generated using the ALEPlot package (Aplet, 2018). </t>
+  </si>
+  <si>
+    <r>
       <rPr>
         <b/>
         <sz val="12"/>
@@ -1092,6 +1119,48 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
+      <t>Code availability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: http://datadryad.org/stash/share/gGubdiD6hCORznmbeHB6gkWoxodyj25Soa3s3yfOfHg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Data availability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: http://datadryad.org/stash/share/gGubdiD6hCORznmbeHB6gkWoxodyj25Soa3s3yfOfHg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
       <t>Authors</t>
     </r>
     <r>
@@ -1101,56 +1170,8 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>: Sarah J. Hart, Asha Paudel, and Maxwell C. Cook</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Title: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Climate-driven decreases in aspen's distribution and opportunities for future expansion across the Southern Rocky Mountains</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Data source</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>: Aspen presence-absence data at 10x10 m spatial resolution were obtained from Cook et al. (2024).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Absence data: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>The Cook et al. (2024) map consists of both presence and absence data.</t>
-    </r>
-  </si>
-  <si>
-    <t>To avoid collinearity between climate predictors, we initially screened the 34 climatic variables at their original resolution (i.e. 1 x 1 km). To this end, we calculated pairwise correlation coefficients and when |r|&gt;0.75, we removed variables based on existing research (Table 5). Where evidence was similar, we used univariate random forest (RF) models to evaluate the potential explanatory power of each predictor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Using the R package DALEX (Biecek 2018), we determined variable importance using a model-agnostic permutation-based approach. In this approach, each variable is randomized and then AUC statistic is compared with the AUC for the full model (where data has not been randomized). We evaluated the relationship between aspen presence and each predictor variable using accumulated local effects (ALE) profiles, which were generated using the ALEPlot package (Aplet, 2018). </t>
+      <t>:</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1161,52 +1182,20 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>Code availability</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>: http://datadryad.org/stash/share/gGubdiD6hCORznmbeHB6gkWoxodyj25Soa3s3yfOfHg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Data availability</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>: http://datadryad.org/stash/share/gGubdiD6hCORznmbeHB6gkWoxodyj25Soa3s3yfOfHg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">DOI: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>10.5061/dryad.t76hdr88v</t>
-    </r>
+      <t>Contact email:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DOI: </t>
   </si>
 </sst>
 </file>
@@ -1358,16 +1347,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1701,47 +1690,47 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
+      <c r="B2" s="15"/>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="15"/>
+      <c r="A4" s="17"/>
       <c r="B4" s="7" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="15"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="16"/>
+      <c r="A6" s="18"/>
       <c r="B6" s="9" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="16" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="16"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="11" t="s">
         <v>5</v>
       </c>
@@ -1751,7 +1740,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
@@ -1763,33 +1752,33 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="15"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="16"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="16" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="13" t="s">
@@ -1797,7 +1786,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="16"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="9" t="s">
         <v>13</v>
       </c>
@@ -1815,7 +1804,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="136" x14ac:dyDescent="0.2">
@@ -1823,27 +1812,27 @@
         <v>17</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="16"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="68" x14ac:dyDescent="0.2">
@@ -1851,95 +1840,95 @@
         <v>19</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A25" s="15"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A26" s="16"/>
+      <c r="A26" s="18"/>
       <c r="B26" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="17"/>
+      <c r="B27" s="15"/>
     </row>
     <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
-        <v>31</v>
+      <c r="A28" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A29" s="15"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="14" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="15"/>
+      <c r="A30" s="17"/>
       <c r="B30" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A31" s="15"/>
+      <c r="A31" s="17"/>
       <c r="B31" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A32" s="15"/>
+      <c r="A32" s="17"/>
       <c r="B32" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A33" s="15"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A34" s="15"/>
+      <c r="A34" s="17"/>
       <c r="B34" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A35" s="15"/>
+      <c r="A35" s="17"/>
       <c r="B35" s="14" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="15"/>
+      <c r="A36" s="17"/>
       <c r="B36" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A37" s="16"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="51" x14ac:dyDescent="0.2">
@@ -1947,160 +1936,155 @@
         <v>28</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="85" x14ac:dyDescent="0.2">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="12" t="s">
+    </row>
+    <row r="40" spans="1:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="A40" s="17"/>
+      <c r="B40" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="85" x14ac:dyDescent="0.2">
+      <c r="A41" s="17"/>
+      <c r="B41" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="102" x14ac:dyDescent="0.2">
+      <c r="A42" s="17"/>
+      <c r="B42" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="A43" s="17"/>
+      <c r="B43" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="204" x14ac:dyDescent="0.2">
+      <c r="A44" s="18"/>
+      <c r="B44" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="68" x14ac:dyDescent="0.2">
-      <c r="A40" s="15"/>
-      <c r="B40" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="85" x14ac:dyDescent="0.2">
-      <c r="A41" s="15"/>
-      <c r="B41" s="12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="102" x14ac:dyDescent="0.2">
-      <c r="A42" s="15"/>
-      <c r="B42" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="68" x14ac:dyDescent="0.2">
-      <c r="A43" s="15"/>
-      <c r="B43" s="12" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" ht="204" x14ac:dyDescent="0.2">
-      <c r="A44" s="16"/>
-      <c r="B44" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B45" s="17"/>
+      <c r="B45" s="15"/>
     </row>
     <row r="46" spans="1:2" ht="102" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="68" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="408" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="102" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="17"/>
+      <c r="B53" s="15"/>
     </row>
     <row r="54" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="17"/>
+      <c r="B56" s="15"/>
     </row>
     <row r="57" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="102" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A39:A44"/>
-    <mergeCell ref="A28:A37"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A2:B2"/>
@@ -2109,6 +2093,11 @@
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A39:A44"/>
+    <mergeCell ref="A28:A37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
